--- a/data/trans_bre/P2A_ner_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,69</t>
+          <t>0,88; 4,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,25</t>
+          <t>-1,1; 3,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 10,83</t>
+          <t>5,4; 11,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,53</t>
+          <t>-2,24; 1,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,84; 336,16</t>
+          <t>25,39; 351,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,47; 110,55</t>
+          <t>-23,58; 124,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,2; 379,35</t>
+          <t>103,63; 406,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-46,76; 50,15</t>
+          <t>-42,17; 64,19</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 3,43</t>
+          <t>-0,18; 3,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,84</t>
+          <t>1,3; 4,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 7,16</t>
+          <t>2,83; 7,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,65</t>
+          <t>1,18; 4,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 147,4</t>
+          <t>-8,98; 142,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,0; 277,39</t>
+          <t>43,84; 277,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,38; 222,82</t>
+          <t>52,34; 220,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,15; 366,92</t>
+          <t>31,92; 382,74</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,24</t>
+          <t>-0,78; 3,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,37</t>
+          <t>0,66; 4,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,13; 9,01</t>
+          <t>3,48; 8,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 54,86</t>
+          <t>0,8; 58,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 123,44</t>
+          <t>-19,39; 124,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,6; 311,72</t>
+          <t>16,84; 289,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,84; 271,89</t>
+          <t>58,79; 268,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,54; 2190,09</t>
+          <t>22,44; 2594,68</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,4</t>
+          <t>0,24; 3,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,67</t>
+          <t>-1,29; 2,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 9,73</t>
+          <t>4,53; 9,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,09</t>
+          <t>-1,61; 1,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 185,54</t>
+          <t>3,31; 205,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 92,04</t>
+          <t>-25,94; 77,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,51; 228,0</t>
+          <t>65,29; 219,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,7; 73,55</t>
+          <t>-31,07; 68,45</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,71</t>
+          <t>0,97; 2,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,93</t>
+          <t>0,9; 2,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,18; 7,74</t>
+          <t>5,24; 7,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 23,61</t>
+          <t>0,93; 23,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,12; 112,13</t>
+          <t>29,09; 114,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,38; 109,49</t>
+          <t>25,21; 106,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>102,14; 197,09</t>
+          <t>104,1; 194,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>24,67; 863,0</t>
+          <t>25,51; 828,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-6,97%</t>
+          <t>-5,88%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,69</t>
+          <t>0,98; 4,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,35</t>
+          <t>-1,14; 3,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,4; 11,14</t>
+          <t>5,1; 10,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 1,7</t>
+          <t>-2,47; 1,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,39; 351,2</t>
+          <t>28,88; 361,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 124,02</t>
+          <t>-22,51; 116,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>103,63; 406,37</t>
+          <t>93,97; 380,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-42,17; 64,19</t>
+          <t>-44,45; 54,68</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>124,8%</t>
+          <t>86,55%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,36</t>
+          <t>-0,29; 3,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,82</t>
+          <t>1,33; 4,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,26</t>
+          <t>2,84; 7,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,7</t>
+          <t>0,68; 3,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 142,64</t>
+          <t>-9,05; 144,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,84; 277,29</t>
+          <t>39,96; 293,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,34; 220,01</t>
+          <t>54,89; 222,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,92; 382,74</t>
+          <t>17,44; 186,82</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22,36</t>
+          <t>1,78</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>658,7%</t>
+          <t>51,16%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,4</t>
+          <t>-0,84; 3,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,23</t>
+          <t>0,7; 4,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,84</t>
+          <t>3,48; 8,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 58,37</t>
+          <t>-0,31; 3,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 124,48</t>
+          <t>-17,92; 134,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,84; 289,85</t>
+          <t>21,15; 355,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,79; 268,24</t>
+          <t>57,21; 271,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,44; 2594,68</t>
+          <t>-7,53; 158,39</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,62</t>
+          <t>0,31; 3,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,47</t>
+          <t>-1,08; 2,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 9,88</t>
+          <t>4,85; 9,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,95</t>
+          <t>-0,66; 2,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 205,72</t>
+          <t>9,21; 202,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,94; 77,34</t>
+          <t>-23,4; 87,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,29; 219,44</t>
+          <t>73,55; 244,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,07; 68,45</t>
+          <t>-17,28; 91,26</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,53</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>199,66%</t>
+          <t>39,07%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,8</t>
+          <t>0,94; 2,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,81</t>
+          <t>0,95; 2,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,24; 7,83</t>
+          <t>5,11; 7,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 23,54</t>
+          <t>0,45; 2,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,09; 114,4</t>
+          <t>28,71; 116,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,21; 106,76</t>
+          <t>26,41; 108,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>104,1; 194,76</t>
+          <t>101,07; 195,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,51; 828,48</t>
+          <t>11,1; 79,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
